--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-Small-3.2-24B-Instruct-2506/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Mistral-Small-3.2-24B-Instruct-2506/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D3">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>426</v>
